--- a/mapping/SB_DWH/Mapping_FCT_LOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_LOS_EXCEPTION.xlsx
@@ -907,7 +907,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr"/>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Ngày dữ liệu</t>
+        </is>
+      </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Ngày ghi nhận PHIÊN BẢN của dòng, không phải ảnh chụp toàn bộ mỗi ngày. Lấy trạng thái tại ngày D bằng ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_BK ORDER BY DAYID DESC) với DAYID &lt;= :ngay, lấy dòng đầu tiên. Không được lọc WHERE DAYID = :ngay.</t>
@@ -935,7 +939,11 @@
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr"/>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ</t>
+        </is>
+      </c>
       <c r="D18" s="28" t="inlineStr"/>
       <c r="E18" s="29" t="inlineStr">
         <is>
@@ -959,7 +967,11 @@
           <t>VARCHAR2(300)</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr"/>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Khóa nghiệp vụ</t>
+        </is>
+      </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
           <t>[CẦN REVIEW] TRẠNG THÁI THIẾT KẾ = CHO_RULE_BA (chưa DA_CHOT). Mô tả gốc: "Khóa nghiệp vụ định danh một lần ghi nhận lý do. Metadata đề xuất ghép EXCEPTION_CATEGORY + EXCEPTION_NAME + RAISED_BY + RAISED_DATE_TIME; database môi trường dev lại đang sinh cột RECID. Danh sách CDC đang hỏi BA/DEV chọn phương án nào. Điền chính thức sau khi chốt khóa nguồn và STG_LOS".</t>
@@ -987,7 +999,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr"/>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>SK hồ sơ</t>
+        </is>
+      </c>
       <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_LOS_APPLICATION. Mặc định -1 nếu không có giá trị phù hợp.</t>
@@ -1015,7 +1031,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr"/>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>SK lý do exception</t>
+        </is>
+      </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_LOS_EXCEPTION_REASON, lấy tên bước phát sinh và cờ vi phạm First Time Right. Mặc định -1 nếu không có giá trị phù hợp.</t>
@@ -1043,7 +1063,11 @@
           <t>NUMBER(18)</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr"/>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>SK người nêu</t>
+        </is>
+      </c>
       <c r="D22" s="28" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_LOS_USER, lookup theo RAISED_BY (người nêu nội dung cần làm rõ). Mặc định -1 nếu không có giá trị phù hợp.</t>
@@ -1071,7 +1095,11 @@
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr"/>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Hệ nguồn</t>
+        </is>
+      </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
           <t>[CẦN REVIEW] Mô tả gốc: "Gán theo tuyến bảng EXCEPTION nguồn/STG_LOS; hậu tố WI_NAME chỉ dùng kiểm tra." — logic gán theo tuyến bảng nguồn/STG_LOS chưa rõ chi tiết kỹ thuật, tạm suy ra literal theo hệ nguồn ETL.</t>
@@ -1099,7 +1127,11 @@
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr"/>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung</t>
+        </is>
+      </c>
       <c r="D24" s="28" t="inlineStr"/>
       <c r="E24" s="29" t="inlineStr">
         <is>
@@ -1123,7 +1155,11 @@
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr"/>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Tên nội dung cần làm rõ</t>
+        </is>
+      </c>
       <c r="D25" s="28" t="inlineStr"/>
       <c r="E25" s="29" t="inlineStr">
         <is>
@@ -1147,7 +1183,11 @@
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr"/>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
       <c r="D26" s="28" t="inlineStr"/>
       <c r="E26" s="29" t="inlineStr">
         <is>
@@ -1171,7 +1211,11 @@
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr"/>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Người nêu</t>
+        </is>
+      </c>
       <c r="D27" s="28" t="inlineStr"/>
       <c r="E27" s="29" t="inlineStr">
         <is>
@@ -1195,7 +1239,11 @@
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr"/>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu</t>
+        </is>
+      </c>
       <c r="D28" s="28" t="inlineStr"/>
       <c r="E28" s="29" t="inlineStr">
         <is>
@@ -1219,7 +1267,11 @@
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr"/>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>Loại ghi nhận</t>
+        </is>
+      </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Raise = lúc bước trả về nêu lý do; Clear = lúc bước nhận đã làm rõ/bổ sung và đẩy lại.</t>
